--- a/4P_Index_Lettre_Politique_Environnement_2016-2020.xlsx
+++ b/4P_Index_Lettre_Politique_Environnement_2016-2020.xlsx
@@ -601,19 +601,15 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>§II.2.2.1: plastic-waste proliferation is symptomatic of persistent bad consumption practices; its eradication remains a priority; §III Programme 3: combat pollution, nuisances and adverse climate-change effects.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document (≠1.0 law, ≠0.75 order/decree).</t>
+          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document with aspirational commitments but no quantifiable plastic targets (≠0.50 plan with targets, ≠0.75 order/decree, ≠1.0 law).</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -629,15 +625,15 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>production, consumption, collection, recycling, disposal</t>
+          <t>production, consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to ~FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
+          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to approximately FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
         </is>
       </c>
       <c r="O2" s="3">
@@ -645,11 +641,11 @@
         <v/>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Disposal</t>
+          <t>Environmental leakage</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -661,11 +657,11 @@
         <v>0</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Policy expects Law banning 0-30 micron plastic bags to help; no standalone plastic-waste strategy in LPSEDD (+0.25 authority via ministerial planning); DPPD operationalisation (+0.25 monitoring). Period expired 2020.</t>
+          <t>Policy expects Law banning 0-30 micron plastic bags to help (+0.25 authority via ministerial planning). Aspirational priority only — no binding obligation. Period expired 2020.</t>
         </is>
       </c>
       <c r="V2" s="3">
@@ -674,7 +670,7 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Most explicit plastic mention — priority to eradicate plastic waste.</t>
+          <t>Most explicit plastic mention — aspirational priority to eradicate plastic waste.</t>
         </is>
       </c>
     </row>
@@ -698,19 +694,15 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>§II.2.2.1: plastic-waste proliferation is symptomatic of persistent bad consumption practices; its eradication remains a priority; §III Programme 3: combat pollution, nuisances and adverse climate-change effects.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document (≠1.0 law, ≠0.75 order/decree).</t>
+          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document with aspirational commitments but no quantifiable plastic targets (≠0.50 plan with targets, ≠0.75 order/decree, ≠1.0 law).</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -726,15 +718,15 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>production, consumption, collection, recycling, disposal</t>
+          <t>production, consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to ~FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
+          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to approximately FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
         </is>
       </c>
       <c r="O3" s="3">
@@ -742,7 +734,7 @@
         <v/>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -758,11 +750,11 @@
         <v>0</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>§II.2.3.1(b): plastic-bag law passed as part of legal reform (+0.25 authority); coastal law in adoption (+0.25 monitoring). Period expired 2020.</t>
+          <t>§II.2.3.1(b): plastic-bag law passed as part of legal reform (+0.25 authority). Informational reference only — not an operative instrument in LPSEDD. Period expired 2020.</t>
         </is>
       </c>
       <c r="V3" s="3">
@@ -771,7 +763,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Reference to Law 2015-09 (thin bags) — direct plastic production/distribution link.</t>
+          <t>Reference to Law 2015-09 (thin bags) — informational, not a regulatory instrument.</t>
         </is>
       </c>
     </row>
@@ -795,19 +787,15 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>§II.2.2.1: plastic-waste proliferation is symptomatic of persistent bad consumption practices; its eradication remains a priority; §III Programme 3: combat pollution, nuisances and adverse climate-change effects.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document (≠1.0 law, ≠0.75 order/decree).</t>
+          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document with aspirational commitments but no quantifiable plastic targets (≠0.50 plan with targets, ≠0.75 order/decree, ≠1.0 law).</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -823,15 +811,15 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>production, consumption, collection, recycling, disposal</t>
+          <t>production, consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to ~FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
+          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to approximately FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
         </is>
       </c>
       <c r="O4" s="3">
@@ -839,11 +827,11 @@
         <v/>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Valorisation</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -855,11 +843,11 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Identified as economic opportunity only; no quantified recycling targets or EPR framework in LPSEDD. Period expired 2020.</t>
+          <t>Identified as economic opportunity only; no quantified recycling targets, EPR framework or binding obligation in LPSEDD. Period expired 2020.</t>
         </is>
       </c>
       <c r="V4" s="3">
@@ -868,7 +856,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Only explicit mention of plastic-waste recycling.</t>
+          <t>Only explicit mention of plastic-waste recycling — voluntary/aspirational.</t>
         </is>
       </c>
     </row>
@@ -892,19 +880,15 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>§II.2.2.1: plastic-waste proliferation is symptomatic of persistent bad consumption practices; its eradication remains a priority; §III Programme 3: combat pollution, nuisances and adverse climate-change effects.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document (≠1.0 law, ≠0.75 order/decree).</t>
+          <t>Sector policy letter validated December 2015 for the 2016-2020 period. Strategic orientation and ministerial planning document with aspirational commitments but no quantifiable plastic targets (≠0.50 plan with targets, ≠0.75 order/decree, ≠1.0 law).</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -920,15 +904,15 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>production, consumption, collection, recycling, disposal</t>
+          <t>production, consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to ~FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
+          <t>§II.2.3.1(c): MEDD budget fell from FCFA 31.25 billion (2011) to approximately FCFA 22 billion (2015); implementation via DPPD budget-programme framework; no dedicated plastic-waste budget line.</t>
         </is>
       </c>
       <c r="O5" s="3">
@@ -936,11 +920,11 @@
         <v/>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Waste management</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -952,11 +936,11 @@
         <v>0</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>§III Programme 3 OS2: improve living-environment quality through rational pollution management (+0.25 authority); absence of filiere approach noted (+0.25 monitoring). Period expired 2020.</t>
+          <t>§III Programme 3 OS2: improve living-environment quality through rational pollution management (+0.25 authority). Planning orientation only — period expired 2020.</t>
         </is>
       </c>
       <c r="V5" s="3">
@@ -965,7 +949,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Living-environment orientation — waste collection/treatment including plastics.</t>
+          <t>Living-environment governance orientation — waste collection/treatment including plastics.</t>
         </is>
       </c>
     </row>
